--- a/history_matching/example/iter2/Cuts/RadiusShouldBe15/test_data.xlsx
+++ b/history_matching/example/iter2/Cuts/RadiusShouldBe15/test_data.xlsx
@@ -2,6 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
     <workbookView activeTab="0"/>
   </bookViews>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
   <si>
     <t>Sample_Id</t>
   </si>
@@ -67,49 +68,52 @@
     <t>Z_Noiseless</t>
   </si>
   <si>
-    <t>Data_20170712_104006.000039</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000040</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000041</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000042</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000043</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000044</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000045</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000046</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000047</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000048</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000049</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000050</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000051</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000052</t>
+    <t>Data_20180119_074635.000040</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000041</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000042</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000043</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000044</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000045</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000046</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000047</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000048</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000049</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000050</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000051</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000052</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000053</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000054</t>
   </si>
 </sst>
 </file>
@@ -458,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -519,52 +523,52 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.802457073701419</v>
+        <v>15.64717327439749</v>
       </c>
       <c r="E2" t="n">
-        <v>4.860002342843856</v>
+        <v>18.91975688719603</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>6.42900344854303</v>
+        <v>25.58656822332529</v>
       </c>
       <c r="H2" t="n">
-        <v>8.011543304523968</v>
+        <v>25.15106084811646</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.582539855980938</v>
+        <v>0.4355073752088323</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000442388450773953</v>
+        <v>2.923253600565564e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>8.011985692974742</v>
+        <v>25.15109008065246</v>
       </c>
       <c r="L2" t="n">
-        <v>1.206070147965007</v>
+        <v>2.091623860924894</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02612319216132164</v>
+        <v>1.710053320126314e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.758915051200491</v>
+        <v>4.871767838190123</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8515002292418729</v>
+        <v>0.2089971020700361</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.049248023012613</v>
+        <v>0.2903176585424796</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -572,52 +576,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
-        <v>18.04667585097297</v>
+        <v>9.633799311327463</v>
       </c>
       <c r="E3" t="n">
-        <v>4.371243625434175</v>
+        <v>-6.313661235264873</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>17.79965879028025</v>
+        <v>12.18767999295959</v>
       </c>
       <c r="H3" t="n">
-        <v>17.91591633776835</v>
+        <v>11.09884679927848</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1162575474881002</v>
+        <v>1.088833193681113</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.002251330165279373</v>
+        <v>1.626742302825558e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>17.91366500760307</v>
+        <v>11.0988630667015</v>
       </c>
       <c r="L3" t="n">
-        <v>1.216404005631173</v>
+        <v>2.091623860770835</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03645705059170723</v>
+        <v>1.710037914154829e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.564948424755754</v>
+        <v>1.872255422161999</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.06123348076945984</v>
+        <v>0.5225510995341628</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.07539577349105361</v>
+        <v>0.7258751924570753</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -625,52 +629,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="n">
-        <v>-16.97539734578124</v>
+        <v>-15.5671355970745</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.812209999606864</v>
+        <v>-15.59915644128273</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>16.92592179524047</v>
+        <v>21.34049442103249</v>
       </c>
       <c r="H4" t="n">
-        <v>17.89667454905515</v>
+        <v>23.15806169431124</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9707527538146792</v>
+        <v>-1.817567273278755</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00201589142912479</v>
+        <v>-4.020486286642919e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>17.89869044048427</v>
+        <v>23.15805767382496</v>
       </c>
       <c r="L4" t="n">
-        <v>1.214555544333699</v>
+        <v>2.091623861089761</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03460858762264252</v>
+        <v>1.71006980679242e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.557320763691766</v>
+        <v>3.915260595749868</v>
       </c>
       <c r="O4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5226197279808166</v>
+        <v>-0.872295106073308</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.6435816792659014</v>
+        <v>-1.211704230539684</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -678,52 +682,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" t="n">
-        <v>12.79733684379762</v>
+        <v>3.214026404672495</v>
       </c>
       <c r="E5" t="n">
-        <v>-8.036268786232</v>
+        <v>-19.64144785367996</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>14.96830751401125</v>
+        <v>19.38330363578894</v>
       </c>
       <c r="H5" t="n">
-        <v>13.70106594387062</v>
+        <v>19.28410547933339</v>
       </c>
       <c r="I5" t="n">
-        <v>1.267241570140634</v>
+        <v>0.09919815645555019</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.002070264655907399</v>
+        <v>-1.190882243077909e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>13.69899567921471</v>
+        <v>19.28409357051096</v>
       </c>
       <c r="L5" t="n">
-        <v>1.211814576928293</v>
+        <v>2.091623861315883</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0318676233291626</v>
+        <v>1.710092419073657e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6992409235514911</v>
+        <v>2.056046109910111</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6822074035098056</v>
+        <v>0.04761344854435327</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8402782207534427</v>
+        <v>0.06613979217433695</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -731,52 +735,52 @@
         <v>22</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" t="n">
-        <v>-6.568787079381316</v>
+        <v>6.119767364281372</v>
       </c>
       <c r="E6" t="n">
-        <v>-17.02641424444721</v>
+        <v>-13.23721378873438</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>19.17574278501695</v>
+        <v>14.0078285523334</v>
       </c>
       <c r="H6" t="n">
-        <v>17.82387929262504</v>
+        <v>13.53155303982732</v>
       </c>
       <c r="I6" t="n">
-        <v>1.351863492391914</v>
+        <v>0.4762755125060849</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003549920880989529</v>
+        <v>-4.585163227495188e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>17.82423428471314</v>
+        <v>13.53155258131099</v>
       </c>
       <c r="L6" t="n">
-        <v>1.209764800808536</v>
+        <v>2.091623861088179</v>
       </c>
       <c r="M6" t="n">
-        <v>0.029817845672369</v>
+        <v>1.710069648600795e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.518369365477752</v>
+        <v>0.7047454854078163</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7266001673981266</v>
+        <v>0.2285770236743846</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8950941486182303</v>
+        <v>0.31751610740688</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -784,52 +788,52 @@
         <v>23</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.35343885374067</v>
+        <v>-19.47431945987062</v>
       </c>
       <c r="E7" t="n">
-        <v>12.95144102572876</v>
+        <v>-0.2446600213936421</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>12.98759110265058</v>
+        <v>20.27629933962165</v>
       </c>
       <c r="H7" t="n">
-        <v>13.10888623431862</v>
+        <v>21.6566651122572</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1212951316680382</v>
+        <v>-1.38036577263555</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0005621765604824767</v>
+        <v>-4.436964712344376e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>13.1094484108791</v>
+        <v>21.65666067529249</v>
       </c>
       <c r="L7" t="n">
-        <v>1.207412870528713</v>
+        <v>2.091623861331974</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02746591530740261</v>
+        <v>1.710094028175136e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.016747025737919</v>
+        <v>3.194701763894714</v>
       </c>
       <c r="O7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.06553540057766377</v>
+        <v>-0.6624707205292423</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.08074686096198996</v>
+        <v>-0.9202373933594901</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -837,52 +841,52 @@
         <v>24</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" t="n">
-        <v>-10.88627057180144</v>
+        <v>-7.754575815394241</v>
       </c>
       <c r="E8" t="n">
-        <v>0.836914015966812</v>
+        <v>22.25927769887195</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>11.17277714941099</v>
+        <v>23.31749142818731</v>
       </c>
       <c r="H8" t="n">
-        <v>10.67045540704322</v>
+        <v>24.86807246913918</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5023217423677693</v>
+        <v>-1.550581040951869</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001376009719921104</v>
+        <v>1.157014334546168e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>10.67183141676314</v>
+        <v>24.86808403928253</v>
       </c>
       <c r="L8" t="n">
-        <v>1.208972553605771</v>
+        <v>2.09162386099755</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02902559749782085</v>
+        <v>1.710060585684051e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.327183399625103</v>
+        <v>4.735945998386963</v>
       </c>
       <c r="O8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2693500890067593</v>
+        <v>-0.744169064877431</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3318303405503223</v>
+        <v>-1.033724479112078</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -890,52 +894,52 @@
         <v>25</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" t="n">
-        <v>14.49472235712129</v>
+        <v>-5.020509047591837</v>
       </c>
       <c r="E9" t="n">
-        <v>4.700955489921441</v>
+        <v>19.40298476679041</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>16.40066142884426</v>
+        <v>20.93111724015277</v>
       </c>
       <c r="H9" t="n">
-        <v>14.2431964464846</v>
+        <v>19.35978639519146</v>
       </c>
       <c r="I9" t="n">
-        <v>2.157464982359656</v>
+        <v>1.571330844961306</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.001950031755195806</v>
+        <v>-2.98359527259058e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>14.24124641472941</v>
+        <v>19.35978341159619</v>
       </c>
       <c r="L9" t="n">
-        <v>1.212888680475968</v>
+        <v>2.091623861135949</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03294172510504723</v>
+        <v>1.710074425637054e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4077382840197788</v>
+        <v>2.092371601159871</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.160424397899528</v>
+        <v>0.7541233057744663</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.429185841382299</v>
+        <v>1.047551904841457</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -943,52 +947,52 @@
         <v>26</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>-12.76776223361325</v>
+        <v>-6.349702508174545</v>
       </c>
       <c r="E10" t="n">
-        <v>9.656624119359236</v>
+        <v>-10.93141576468926</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>17.07083147099415</v>
+        <v>12.96369530722316</v>
       </c>
       <c r="H10" t="n">
-        <v>15.51777103363878</v>
+        <v>11.61675283589148</v>
       </c>
       <c r="I10" t="n">
-        <v>1.55306043735537</v>
+        <v>1.346942471331685</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001786235631568567</v>
+        <v>9.135959117481869e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>15.51955726927035</v>
+        <v>11.61676197185059</v>
       </c>
       <c r="L10" t="n">
-        <v>1.211143856721268</v>
+        <v>2.091623860844935</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03119690157473087</v>
+        <v>1.710045324203274e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2792695597162807</v>
+        <v>1.623702487484223</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8338323586984694</v>
+        <v>0.6464277679912854</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.027086930097474</v>
+        <v>0.8979521446129366</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -996,52 +1000,52 @@
         <v>27</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" t="n">
-        <v>-18.27912209909559</v>
+        <v>11.55208325397895</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.944458757879715</v>
+        <v>-2.594142965282529</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
       </c>
       <c r="G11" t="n">
-        <v>18.60959621750342</v>
+        <v>11.43399179771512</v>
       </c>
       <c r="H11" t="n">
-        <v>19.06990158067117</v>
+        <v>11.39729173850003</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4603053631677518</v>
+        <v>0.03670005921508945</v>
       </c>
       <c r="J11" t="n">
-        <v>0.002178799604774017</v>
+        <v>2.774891475946241e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>19.07208038027595</v>
+        <v>11.39731948741479</v>
       </c>
       <c r="L11" t="n">
-        <v>1.215779434148578</v>
+        <v>2.091623860676256</v>
       </c>
       <c r="M11" t="n">
-        <v>0.035832479596138</v>
+        <v>1.710028456361157e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>2.187337919745525</v>
+        <v>1.72901855008082</v>
       </c>
       <c r="O11" t="b">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2484256331024478</v>
+        <v>0.01759997994884421</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.3058966137213813</v>
+        <v>0.02444811396268451</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1049,52 +1053,52 @@
         <v>28</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>5.293972429829942</v>
+        <v>8.905195128274912</v>
       </c>
       <c r="E12" t="n">
-        <v>6.365898892891295</v>
+        <v>0.6328811691435305</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>9.05861654609622</v>
+        <v>10.27283668761884</v>
       </c>
       <c r="H12" t="n">
-        <v>9.003631429751238</v>
+        <v>8.954642541697012</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05498511634498193</v>
+        <v>1.318194145921828</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0008347564541903819</v>
+        <v>1.158022684317322e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>9.002796673297047</v>
+        <v>8.954654121923856</v>
       </c>
       <c r="L12" t="n">
-        <v>1.20703661158382</v>
+        <v>2.091623860796858</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02708965539932251</v>
+        <v>1.710040516519658e-05</v>
       </c>
       <c r="N12" t="n">
-        <v>3.225498050615997</v>
+        <v>2.901316152844923</v>
       </c>
       <c r="O12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.03002180868167242</v>
+        <v>0.6326295380582111</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.03699123197335128</v>
+        <v>0.8787850376740686</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1102,52 +1106,52 @@
         <v>29</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>12.22880817625474</v>
+        <v>12.32981511623489</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.67210910750039</v>
+        <v>-5.976887175569317</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>18.68397907897687</v>
+        <v>14.56697603070205</v>
       </c>
       <c r="H13" t="n">
-        <v>17.28377767796565</v>
+        <v>13.2571630595462</v>
       </c>
       <c r="I13" t="n">
-        <v>1.400201401011223</v>
+        <v>1.309812971155848</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.002131857505122739</v>
+        <v>2.78623868930194e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>17.28164582046052</v>
+        <v>13.25719092193309</v>
       </c>
       <c r="L13" t="n">
-        <v>1.212545514853268</v>
+        <v>2.091623860665208</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03259855881333351</v>
+        <v>1.710027351554951e-05</v>
       </c>
       <c r="N13" t="n">
-        <v>1.226169430031024</v>
+        <v>0.8364186651312152</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7536218622930168</v>
+        <v>0.6285993836458637</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9281891299500237</v>
+        <v>0.873186754356201</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1155,52 +1159,52 @@
         <v>30</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1188645956767829</v>
+        <v>-8.022617576777357</v>
       </c>
       <c r="E14" t="n">
-        <v>13.3061506418337</v>
+        <v>-0.9540166085869116</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>14.726582869176</v>
+        <v>7.498060208961257</v>
       </c>
       <c r="H14" t="n">
-        <v>13.06296007104334</v>
+        <v>8.937729065488384</v>
       </c>
       <c r="I14" t="n">
-        <v>1.663622798132664</v>
+        <v>-1.439668856527127</v>
       </c>
       <c r="J14" t="n">
-        <v>6.76455161975205e-05</v>
+        <v>1.600749453780932e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>13.06302771655953</v>
+        <v>8.937745072982921</v>
       </c>
       <c r="L14" t="n">
-        <v>1.207290945027</v>
+        <v>2.091623860664242</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02734399028122425</v>
+        <v>1.710027254915733e-05</v>
       </c>
       <c r="N14" t="n">
-        <v>1.041730649386163</v>
+        <v>2.909431238082331</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8946831114933257</v>
+        <v>-0.6909415995872621</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.102358616910762</v>
+        <v>-0.9597862621087788</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1208,52 +1212,105 @@
         <v>31</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>6.471070127194388</v>
+        <v>1.271972223678517</v>
       </c>
       <c r="E15" t="n">
-        <v>13.6042750421316</v>
+        <v>4.762936393809142</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>16.54212208475527</v>
+        <v>6.8964270541306</v>
       </c>
       <c r="H15" t="n">
-        <v>14.72714335949274</v>
+        <v>6.784676958159253</v>
       </c>
       <c r="I15" t="n">
-        <v>1.814978725262527</v>
+        <v>0.1117500959713471</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0008097575859299556</v>
+        <v>-3.657918562355292e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>14.72633360190681</v>
+        <v>6.784640378973629</v>
       </c>
       <c r="L15" t="n">
-        <v>1.208979787355518</v>
+        <v>2.091623861277785</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02903283201158047</v>
+        <v>1.710088609260215e-05</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1471456623016457</v>
+        <v>3.942761266155861</v>
       </c>
       <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.05364928538894415</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.07452416689867654</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="C16" t="n">
+        <v>54</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5.901819438052478</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-14.97917087907612</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="n">
+        <v>17.10117035284206</v>
+      </c>
+      <c r="H16" t="n">
+        <v>15.0568084410487</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.044361911793359</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-8.370095190947601e-07</v>
+      </c>
+      <c r="K16" t="n">
+        <v>15.05680760403918</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.09162386113079</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.710073909778003e-05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.02726342256026723</v>
+      </c>
+      <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P15" t="n">
-        <v>0.9763178847315278</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.202790386665715</v>
+      <c r="P16" t="n">
+        <v>0.9811419867072542</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.362903319955296</v>
       </c>
     </row>
   </sheetData>

--- a/history_matching/example/iter2/Cuts/RadiusShouldBe15/test_data.xlsx
+++ b/history_matching/example/iter2/Cuts/RadiusShouldBe15/test_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="32">
   <si>
     <t>Sample_Id</t>
   </si>
@@ -68,52 +68,49 @@
     <t>Z_Noiseless</t>
   </si>
   <si>
-    <t>Data_20180119_074635.000040</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000041</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000042</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000043</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000044</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000045</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000046</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000047</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000048</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000049</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000050</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000051</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000052</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000053</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000054</t>
+    <t>Data_20180120_214437.000039</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000040</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000041</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000042</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000043</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000044</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000045</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000046</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000047</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000048</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000049</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000050</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000051</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000052</t>
   </si>
 </sst>
 </file>
@@ -462,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -523,52 +520,52 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="n">
-        <v>15.64717327439749</v>
+        <v>-32.11547826583482</v>
       </c>
       <c r="E2" t="n">
-        <v>18.91975688719603</v>
+        <v>-7.654971405325099</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>25.58656822332529</v>
+        <v>32.73994135871285</v>
       </c>
       <c r="H2" t="n">
-        <v>25.15106084811646</v>
+        <v>30.59665798645355</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4355073752088323</v>
+        <v>2.143283372259294</v>
       </c>
       <c r="J2" t="n">
-        <v>2.923253600565564e-05</v>
+        <v>2.683889965556531</v>
       </c>
       <c r="K2" t="n">
-        <v>25.15109008065246</v>
+        <v>33.28054795201008</v>
       </c>
       <c r="L2" t="n">
-        <v>2.091623860924894</v>
+        <v>0.8330002793859127</v>
       </c>
       <c r="M2" t="n">
-        <v>1.710053320126314e-05</v>
+        <v>0.123860327494768</v>
       </c>
       <c r="N2" t="n">
-        <v>4.871767838190123</v>
+        <v>10.41123926641803</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2089971020700361</v>
+        <v>-0.3078892715139736</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2903176585424796</v>
+        <v>-0.3508760755177283</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -576,52 +573,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="n">
-        <v>9.633799311327463</v>
+        <v>-17.2210854147443</v>
       </c>
       <c r="E3" t="n">
-        <v>-6.313661235264873</v>
+        <v>14.37122469349954</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>12.18767999295959</v>
+        <v>21.09146970262135</v>
       </c>
       <c r="H3" t="n">
-        <v>11.09884679927848</v>
+        <v>24.03973872680498</v>
       </c>
       <c r="I3" t="n">
-        <v>1.088833193681113</v>
+        <v>-2.948269024183634</v>
       </c>
       <c r="J3" t="n">
-        <v>1.626742302825558e-05</v>
+        <v>-1.660495082560339</v>
       </c>
       <c r="K3" t="n">
-        <v>11.0988630667015</v>
+        <v>22.37924364424465</v>
       </c>
       <c r="L3" t="n">
-        <v>2.091623860770835</v>
+        <v>0.9751191389098802</v>
       </c>
       <c r="M3" t="n">
-        <v>1.710037914154829e-05</v>
+        <v>0.2659791870187355</v>
       </c>
       <c r="N3" t="n">
-        <v>1.872255422161999</v>
+        <v>4.109026750900323</v>
       </c>
       <c r="O3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5225510995341628</v>
+        <v>-0.7170785828937247</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7258751924570753</v>
+        <v>-0.8118692839302164</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -629,52 +626,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" t="n">
-        <v>-15.5671355970745</v>
+        <v>-35.12251974097423</v>
       </c>
       <c r="E4" t="n">
-        <v>-15.59915644128273</v>
+        <v>-1.513590034678785</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>21.34049442103249</v>
+        <v>37.1835025800134</v>
       </c>
       <c r="H4" t="n">
-        <v>23.15806169431124</v>
+        <v>31.62225508449954</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.817567273278755</v>
+        <v>5.561247495513864</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.020486286642919e-06</v>
+        <v>3.993697024016907</v>
       </c>
       <c r="K4" t="n">
-        <v>23.15805767382496</v>
+        <v>35.61595210851645</v>
       </c>
       <c r="L4" t="n">
-        <v>2.091623861089761</v>
+        <v>0.8187868771681437</v>
       </c>
       <c r="M4" t="n">
-        <v>1.71006980679242e-05</v>
+        <v>0.1096469252769989</v>
       </c>
       <c r="N4" t="n">
-        <v>3.915260595749868</v>
+        <v>11.76847075623576</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.872295106073308</v>
+        <v>0.894825123071313</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.211704230539684</v>
+        <v>1.020464781627198</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -682,52 +679,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" t="n">
-        <v>3.214026404672495</v>
+        <v>-16.21642663769896</v>
       </c>
       <c r="E5" t="n">
-        <v>-19.64144785367996</v>
+        <v>8.592593585022641</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>19.38330363578894</v>
+        <v>18.40345657952444</v>
       </c>
       <c r="H5" t="n">
-        <v>19.28410547933339</v>
+        <v>23.81305347050009</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09919815645555019</v>
+        <v>-5.409596890975649</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.190882243077909e-05</v>
+        <v>-5.770269025398099</v>
       </c>
       <c r="K5" t="n">
-        <v>19.28409357051096</v>
+        <v>18.04278444510199</v>
       </c>
       <c r="L5" t="n">
-        <v>2.091623861315883</v>
+        <v>0.7632331995740652</v>
       </c>
       <c r="M5" t="n">
-        <v>1.710092419073657e-05</v>
+        <v>0.05409324768292047</v>
       </c>
       <c r="N5" t="n">
-        <v>2.056046109910111</v>
+        <v>1.752890613894672</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04761344854435327</v>
+        <v>0.2077764003757029</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06613979217433695</v>
+        <v>0.2376088237300586</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -735,52 +732,52 @@
         <v>22</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" t="n">
-        <v>6.119767364281372</v>
+        <v>0.7704114866391123</v>
       </c>
       <c r="E6" t="n">
-        <v>-13.23721378873438</v>
+        <v>21.65364319293591</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>14.0078285523334</v>
+        <v>21.85086396069195</v>
       </c>
       <c r="H6" t="n">
-        <v>13.53155303982732</v>
+        <v>16.60269964887338</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4762755125060849</v>
+        <v>5.24816431181857</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.585163227495188e-07</v>
+        <v>4.524602882659829</v>
       </c>
       <c r="K6" t="n">
-        <v>13.53155258131099</v>
+        <v>21.12730253153321</v>
       </c>
       <c r="L6" t="n">
-        <v>2.091623861088179</v>
+        <v>0.9585435520808012</v>
       </c>
       <c r="M6" t="n">
-        <v>1.710069648600795e-05</v>
+        <v>0.2494036001896565</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7047454854078163</v>
+        <v>3.420702889701499</v>
       </c>
       <c r="O6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2285770236743846</v>
+        <v>0.4039442575035564</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.31751610740688</v>
+        <v>0.4576750233532845</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -788,52 +785,52 @@
         <v>23</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" t="n">
-        <v>-19.47431945987062</v>
+        <v>-12.41431378212511</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2446600213936421</v>
+        <v>13.65131719693666</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>20.27629933962165</v>
+        <v>18.54654793798706</v>
       </c>
       <c r="H7" t="n">
-        <v>21.6566651122572</v>
+        <v>22.14018619096051</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.38036577263555</v>
+        <v>-3.593638252973452</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.436964712344376e-06</v>
+        <v>-4.203557500896221</v>
       </c>
       <c r="K7" t="n">
-        <v>21.65666067529249</v>
+        <v>17.93662869006429</v>
       </c>
       <c r="L7" t="n">
-        <v>2.091623861331974</v>
+        <v>0.8235961270903288</v>
       </c>
       <c r="M7" t="n">
-        <v>1.710094028175136e-05</v>
+        <v>0.1144561751991841</v>
       </c>
       <c r="N7" t="n">
-        <v>3.194701763894714</v>
+        <v>1.675041754180436</v>
       </c>
       <c r="O7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6624707205292423</v>
+        <v>0.3478956023298262</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9202373933594901</v>
+        <v>0.3966493114089073</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -841,52 +838,52 @@
         <v>24</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.754575815394241</v>
+        <v>-32.95688512640088</v>
       </c>
       <c r="E8" t="n">
-        <v>22.25927769887195</v>
+        <v>-2.510929373411969</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>23.31749142818731</v>
+        <v>32.63951692735998</v>
       </c>
       <c r="H8" t="n">
-        <v>24.86807246913918</v>
+        <v>30.78988512223815</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.550581040951869</v>
+        <v>1.849631805121824</v>
       </c>
       <c r="J8" t="n">
-        <v>1.157014334546168e-05</v>
+        <v>2.774375181382137</v>
       </c>
       <c r="K8" t="n">
-        <v>24.86808403928253</v>
+        <v>33.56426030362029</v>
       </c>
       <c r="L8" t="n">
-        <v>2.09162386099755</v>
+        <v>0.8273022453254814</v>
       </c>
       <c r="M8" t="n">
-        <v>1.710060585684051e-05</v>
+        <v>0.1181622934343366</v>
       </c>
       <c r="N8" t="n">
-        <v>4.735945998386963</v>
+        <v>10.5826046659903</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.744169064877431</v>
+        <v>-0.5271523566466868</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.033724479112078</v>
+        <v>-0.6009183945729563</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -894,52 +891,52 @@
         <v>25</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.020509047591837</v>
+        <v>-28.92875655404802</v>
       </c>
       <c r="E9" t="n">
-        <v>19.40298476679041</v>
+        <v>-2.639948799684234</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>20.93111724015277</v>
+        <v>29.56602724456997</v>
       </c>
       <c r="H9" t="n">
-        <v>19.35978639519146</v>
+        <v>29.19561729356374</v>
       </c>
       <c r="I9" t="n">
-        <v>1.571330844961306</v>
+        <v>0.3704099510062342</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.98359527259058e-06</v>
+        <v>0.3101545430739843</v>
       </c>
       <c r="K9" t="n">
-        <v>19.35978341159619</v>
+        <v>29.50577183663772</v>
       </c>
       <c r="L9" t="n">
-        <v>2.091623861135949</v>
+        <v>0.8178733949472519</v>
       </c>
       <c r="M9" t="n">
-        <v>1.710074425637054e-05</v>
+        <v>0.1087334430561071</v>
       </c>
       <c r="N9" t="n">
-        <v>2.092371601159871</v>
+        <v>8.281750174163948</v>
       </c>
       <c r="O9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7541233057744663</v>
+        <v>0.03440149485026606</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.047551904841457</v>
+        <v>0.0392334589509887</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -947,52 +944,52 @@
         <v>26</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.349702508174545</v>
+        <v>-21.22137915573253</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.93141576468926</v>
+        <v>6.490156678409704</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>12.96369530722316</v>
+        <v>21.15111311044681</v>
       </c>
       <c r="H10" t="n">
-        <v>11.61675283589148</v>
+        <v>25.87047470227871</v>
       </c>
       <c r="I10" t="n">
-        <v>1.346942471331685</v>
+        <v>-4.719361591831895</v>
       </c>
       <c r="J10" t="n">
-        <v>9.135959117481869e-06</v>
+        <v>-3.65761737764893</v>
       </c>
       <c r="K10" t="n">
-        <v>11.61676197185059</v>
+        <v>22.21285732462978</v>
       </c>
       <c r="L10" t="n">
-        <v>2.091623860844935</v>
+        <v>0.7765547866339209</v>
       </c>
       <c r="M10" t="n">
-        <v>1.710045324203274e-05</v>
+        <v>0.06741483474277611</v>
       </c>
       <c r="N10" t="n">
-        <v>1.623702487484223</v>
+        <v>4.146036027886757</v>
       </c>
       <c r="O10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6464277679912854</v>
+        <v>-0.6103031803181879</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8979521446129366</v>
+        <v>-0.6974579222462055</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1000,52 +997,52 @@
         <v>27</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" t="n">
-        <v>11.55208325397895</v>
+        <v>-25.43299411658989</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.594142965282529</v>
+        <v>-14.98760651516247</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
       </c>
       <c r="G11" t="n">
-        <v>11.43399179771512</v>
+        <v>31.47507357129949</v>
       </c>
       <c r="H11" t="n">
-        <v>11.39729173850003</v>
+        <v>28.16173910969011</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03670005921508945</v>
+        <v>3.313334461609376</v>
       </c>
       <c r="J11" t="n">
-        <v>2.774891475946241e-05</v>
+        <v>1.558683040097657</v>
       </c>
       <c r="K11" t="n">
-        <v>11.39731948741479</v>
+        <v>29.72042214978777</v>
       </c>
       <c r="L11" t="n">
-        <v>2.091623860676256</v>
+        <v>1.024197332710009</v>
       </c>
       <c r="M11" t="n">
-        <v>1.710028456361157e-05</v>
+        <v>0.315057380818864</v>
       </c>
       <c r="N11" t="n">
-        <v>1.72901855008082</v>
+        <v>8.135192606320601</v>
       </c>
       <c r="O11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01759997994884421</v>
+        <v>0.9697023037588531</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.02444811396268451</v>
+        <v>1.09557549611853</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1053,52 +1050,52 @@
         <v>28</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>8.905195128274912</v>
+        <v>-6.904847289375829</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6328811691435305</v>
+        <v>-18.4307280362564</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>10.27283668761884</v>
+        <v>20.56889095849385</v>
       </c>
       <c r="H12" t="n">
-        <v>8.954642541697012</v>
+        <v>20.96536787612351</v>
       </c>
       <c r="I12" t="n">
-        <v>1.318194145921828</v>
+        <v>-0.3964769176296628</v>
       </c>
       <c r="J12" t="n">
-        <v>1.158022684317322e-05</v>
+        <v>-1.32611776029672</v>
       </c>
       <c r="K12" t="n">
-        <v>8.954654121923856</v>
+        <v>19.63925011582679</v>
       </c>
       <c r="L12" t="n">
-        <v>2.091623860796858</v>
+        <v>1.55173640740823</v>
       </c>
       <c r="M12" t="n">
-        <v>1.710040516519658e-05</v>
+        <v>0.8425964555170851</v>
       </c>
       <c r="N12" t="n">
-        <v>2.901316152844923</v>
+        <v>2.379341537214537</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6326295380582111</v>
+        <v>0.476786768642381</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8787850376740686</v>
+        <v>0.5286321457963151</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1106,52 +1103,52 @@
         <v>29</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>12.32981511623489</v>
+        <v>-27.82371049578684</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.976887175569317</v>
+        <v>4.827542519883039</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>14.56697603070205</v>
+        <v>30.63957559157354</v>
       </c>
       <c r="H13" t="n">
-        <v>13.2571630595462</v>
+        <v>28.54730395130411</v>
       </c>
       <c r="I13" t="n">
-        <v>1.309812971155848</v>
+        <v>2.092271640269431</v>
       </c>
       <c r="J13" t="n">
-        <v>2.78623868930194e-05</v>
+        <v>0.3355860496844929</v>
       </c>
       <c r="K13" t="n">
-        <v>13.25719092193309</v>
+        <v>28.8828900009886</v>
       </c>
       <c r="L13" t="n">
-        <v>2.091623860665208</v>
+        <v>0.8183533876705136</v>
       </c>
       <c r="M13" t="n">
-        <v>1.710027351554951e-05</v>
+        <v>0.1092134357793688</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8364186651312152</v>
+        <v>7.925509562332002</v>
       </c>
       <c r="O13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6285993836458637</v>
+        <v>1.002862404384125</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.873186754356201</v>
+        <v>1.143695526850571</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1159,52 +1156,52 @@
         <v>30</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.022617576777357</v>
+        <v>11.39004839295535</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9540166085869116</v>
+        <v>-17.05978737646872</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>7.498060208961257</v>
+        <v>20.64054628935165</v>
       </c>
       <c r="H14" t="n">
-        <v>8.937729065488384</v>
+        <v>13.71390019552832</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.439668856527127</v>
+        <v>6.926646093823326</v>
       </c>
       <c r="J14" t="n">
-        <v>1.600749453780932e-05</v>
+        <v>7.010042205593044</v>
       </c>
       <c r="K14" t="n">
-        <v>8.937745072982921</v>
+        <v>20.72394240112137</v>
       </c>
       <c r="L14" t="n">
-        <v>2.091623860664242</v>
+        <v>1.118155510561357</v>
       </c>
       <c r="M14" t="n">
-        <v>1.710027254915733e-05</v>
+        <v>0.4090155586702118</v>
       </c>
       <c r="N14" t="n">
-        <v>2.909431238082331</v>
+        <v>3.118883748237522</v>
       </c>
       <c r="O14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6909415995872621</v>
+        <v>-0.04544119409968573</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9597862621087788</v>
+        <v>-0.05114290151863748</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1212,105 +1209,52 @@
         <v>31</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>1.271972223678517</v>
+        <v>-1.471629036094555</v>
       </c>
       <c r="E15" t="n">
-        <v>4.762936393809142</v>
+        <v>15.13391593356201</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>6.8964270541306</v>
+        <v>15.33346870870436</v>
       </c>
       <c r="H15" t="n">
-        <v>6.784676958159253</v>
+        <v>17.71752814480915</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1117500959713471</v>
+        <v>-2.384059436104794</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.657918562355292e-05</v>
+        <v>-3.381456962446516</v>
       </c>
       <c r="K15" t="n">
-        <v>6.784640378973629</v>
+        <v>14.33607118236264</v>
       </c>
       <c r="L15" t="n">
-        <v>2.091623861277785</v>
+        <v>0.8102973949416148</v>
       </c>
       <c r="M15" t="n">
-        <v>1.710088609260215e-05</v>
+        <v>0.1011574430504701</v>
       </c>
       <c r="N15" t="n">
-        <v>3.942761266155861</v>
+        <v>0.3795244007274867</v>
       </c>
       <c r="O15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.05364928538894415</v>
+        <v>0.5701465103126115</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.07452416689867654</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="C16" t="n">
-        <v>54</v>
-      </c>
-      <c r="D16" t="n">
-        <v>5.901819438052478</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-14.97917087907612</v>
-      </c>
-      <c r="F16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" t="n">
-        <v>17.10117035284206</v>
-      </c>
-      <c r="H16" t="n">
-        <v>15.0568084410487</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.044361911793359</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-8.370095190947601e-07</v>
-      </c>
-      <c r="K16" t="n">
-        <v>15.05680760403918</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2.09162386113079</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.710073909778003e-05</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.02726342256026723</v>
-      </c>
-      <c r="O16" t="b">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.9811419867072542</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.362903319955296</v>
+        <v>0.6504702384319236</v>
       </c>
     </row>
   </sheetData>
